--- a/data/bill_template.xlsx
+++ b/data/bill_template.xlsx
@@ -680,7 +680,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -707,6 +707,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1512,18 +1515,54 @@
           <t>如分辨率/std&amp;pro模式等</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>图片按次计费时的调用张数</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>视频/音频按时长计费时的秒数</t>
+        </is>
+      </c>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
-      <c r="U2" s="6" t="n"/>
+      <c r="U2" s="12" t="inlineStr">
+        <is>
+          <t>如：token、张、秒</t>
+        </is>
+      </c>
       <c r="V2" s="6" t="n"/>
-      <c r="W2" s="6" t="n"/>
-      <c r="X2" s="6" t="n"/>
-      <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n"/>
-      <c r="AA2" s="4" t="n"/>
-      <c r="AB2" s="4" t="n"/>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>本币，= 总金额 × 折扣</t>
+        </is>
+      </c>
+      <c r="X2" s="6" t="inlineStr">
+        <is>
+          <t>本币，= 总金额 × 折扣 ÷ 汇率</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>阶梯模型自动带入：缓存未命中(输入)单价，同 E</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>阶梯模型自动带入：缓存读单价，同 G</t>
+        </is>
+      </c>
+      <c r="AA2" s="4" t="inlineStr">
+        <is>
+          <t>阶梯模型自动带入：输出单价，同 I</t>
+        </is>
+      </c>
+      <c r="AB2" s="4" t="inlineStr">
+        <is>
+          <t>阶梯计费模型注明本行命中的档位</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/bill_template.xlsx
+++ b/data/bill_template.xlsx
@@ -680,7 +680,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -708,6 +708,12 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1309,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.3333333333333" defaultRowHeight="16.5"/>
   <cols>
     <col width="11.3333333333333" customWidth="1" style="1" min="1" max="1"/>
@@ -1477,6 +1483,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>官方刊例（美金）</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40.5" customHeight="1" s="11">
       <c r="A2" s="4" t="n"/>
@@ -1532,15 +1543,19 @@
           <t>如：token、张、秒</t>
         </is>
       </c>
-      <c r="V2" s="6" t="n"/>
+      <c r="V2" s="6" t="inlineStr">
+        <is>
+          <t>本币，= 总金额 × 折扣</t>
+        </is>
+      </c>
       <c r="W2" s="6" t="inlineStr">
         <is>
-          <t>本币，= 总金额 × 折扣</t>
+          <t>美金，= 结算金额（人民币） ÷ 汇率</t>
         </is>
       </c>
       <c r="X2" s="6" t="inlineStr">
         <is>
-          <t>本币，= 总金额 × 折扣 ÷ 汇率</t>
+          <t>“是”= 本行单价×用量可还原原厂刊例</t>
         </is>
       </c>
       <c r="Y2" s="4" t="inlineStr">
@@ -1560,7 +1575,12 @@
       </c>
       <c r="AB2" s="4" t="inlineStr">
         <is>
-          <t>阶梯计费模型注明本行命中的档位</t>
+          <t>阶梯计费模型注明本行命中的档位；跨档行注明单价不适用；折扣为反推值时在此注明</t>
+        </is>
+      </c>
+      <c r="AC2" s="14" t="inlineStr">
+        <is>
+          <t>单档行=按单价×用量之和自动核算；跨档行/按次计费行按表达式或按次单价现算，供 S 列换算人民币引用，不可编辑</t>
         </is>
       </c>
     </row>
